--- a/Chấm công/CHẤM CÔNG T1 2026.xlsx
+++ b/Chấm công/CHẤM CÔNG T1 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Chấm công\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B84DD1-BB30-4AC3-8F4D-3D8E171F85E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A57B94-64DD-4645-8034-D973B567BCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="487" activeTab="2" xr2:uid="{5BB9A907-C889-48BA-A08B-CDCC7DB0058E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="487" activeTab="1" xr2:uid="{5BB9A907-C889-48BA-A08B-CDCC7DB0058E}"/>
   </bookViews>
   <sheets>
     <sheet name="DƯƠNG ĐÔNG" sheetId="13" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="53">
   <si>
     <t>DOANH THU</t>
   </si>
@@ -170,12 +170,42 @@
   <si>
     <t>NGUYỄN ĐĂNG KHÁNH</t>
   </si>
+  <si>
+    <t>nghỉ bệnh</t>
+  </si>
+  <si>
+    <t>nghỉ luôn</t>
+  </si>
+  <si>
+    <t>HUỲNH VIỆT CHƯƠNG</t>
+  </si>
+  <si>
+    <t>XIN NGHỈ 1 HÔM</t>
+  </si>
+  <si>
+    <t>TẠM NGHỈ</t>
+  </si>
+  <si>
+    <t>NGHỈ DO NHÀ XA</t>
+  </si>
+  <si>
+    <t>NGHỈ CHĂM CON</t>
+  </si>
+  <si>
+    <t>LƯ HỚN VINH</t>
+  </si>
+  <si>
+    <t>VÕ ĐẸP</t>
+  </si>
+  <si>
+    <t>NGHỈ BỆNH</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="13"/>
       <color theme="1"/>
@@ -247,8 +277,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -315,8 +351,26 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -427,13 +481,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -523,14 +588,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -554,6 +619,68 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="4" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -582,6 +709,7 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
+      <sheetName val="biển số xe"/>
       <sheetName val="01-01"/>
       <sheetName val="02-01"/>
       <sheetName val="03-01"/>
@@ -603,29 +731,50 @@
       <sheetName val="18-01"/>
       <sheetName val="19-01"/>
       <sheetName val="20-01"/>
+      <sheetName val="21-01"/>
+      <sheetName val="22-01"/>
+      <sheetName val="23-01"/>
+      <sheetName val="24-01"/>
+      <sheetName val="25-01"/>
+      <sheetName val="26-01"/>
+      <sheetName val="27-01"/>
+      <sheetName val="28-01"/>
+      <sheetName val="29-01"/>
+      <sheetName val="30-01"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
+      <sheetData sheetId="30"/>
+      <sheetData sheetId="31"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1683,7 +1832,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95551214-BA74-44A9-8CA1-20E853762A71}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:AT45"/>
+  <dimension ref="A2:AU45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="13.33203125" customWidth="1"/>
@@ -1713,6 +1862,18 @@
     <col min="29" max="29" width="13.77734375" customWidth="1"/>
     <col min="30" max="30" width="13.6640625" customWidth="1"/>
     <col min="31" max="31" width="12.5546875" customWidth="1"/>
+    <col min="32" max="32" width="13.21875" customWidth="1"/>
+    <col min="33" max="33" width="12.5546875" customWidth="1"/>
+    <col min="34" max="34" width="12.44140625" customWidth="1"/>
+    <col min="35" max="35" width="11.6640625" customWidth="1"/>
+    <col min="36" max="36" width="12" customWidth="1"/>
+    <col min="37" max="37" width="14.5546875" customWidth="1"/>
+    <col min="38" max="38" width="13.77734375" customWidth="1"/>
+    <col min="39" max="39" width="12.77734375" customWidth="1"/>
+    <col min="40" max="40" width="15.44140625" customWidth="1"/>
+    <col min="41" max="41" width="13.88671875" customWidth="1"/>
+    <col min="42" max="42" width="14.109375" customWidth="1"/>
+    <col min="43" max="43" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:46" ht="27.75" x14ac:dyDescent="0.25">
@@ -1802,6 +1963,30 @@
         <v>25</v>
       </c>
       <c r="AE6" s="30"/>
+      <c r="AF6" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AG6" s="30"/>
+      <c r="AH6" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI6" s="30"/>
+      <c r="AJ6" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="AM6" s="30"/>
+      <c r="AN6" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO6" s="30"/>
+      <c r="AP6" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="AQ6" s="30"/>
       <c r="AT6" t="s">
         <v>33</v>
       </c>
@@ -1895,6 +2080,42 @@
         <v>0</v>
       </c>
       <c r="AE7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1981,6 +2202,18 @@
       <c r="AC8" s="8"/>
       <c r="AD8" s="5"/>
       <c r="AE8" s="5"/>
+      <c r="AF8" s="8"/>
+      <c r="AG8" s="8"/>
+      <c r="AH8" s="8"/>
+      <c r="AI8" s="8"/>
+      <c r="AJ8" s="8"/>
+      <c r="AK8" s="8"/>
+      <c r="AL8" s="8"/>
+      <c r="AM8" s="8"/>
+      <c r="AN8" s="8"/>
+      <c r="AO8" s="8"/>
+      <c r="AP8" s="8"/>
+      <c r="AQ8" s="8"/>
     </row>
     <row r="9" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
@@ -2068,6 +2301,18 @@
       <c r="AE9" s="5">
         <v>690000</v>
       </c>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="25"/>
+      <c r="AH9" s="8"/>
+      <c r="AI9" s="8"/>
+      <c r="AJ9" s="8"/>
+      <c r="AK9" s="8"/>
+      <c r="AL9" s="8"/>
+      <c r="AM9" s="8"/>
+      <c r="AN9" s="8"/>
+      <c r="AO9" s="8"/>
+      <c r="AP9" s="8"/>
+      <c r="AQ9" s="8"/>
     </row>
     <row r="10" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
@@ -2155,6 +2400,18 @@
       <c r="AE10" s="5">
         <v>1020000</v>
       </c>
+      <c r="AF10" s="8"/>
+      <c r="AG10" s="8"/>
+      <c r="AH10" s="8"/>
+      <c r="AI10" s="8"/>
+      <c r="AJ10" s="8"/>
+      <c r="AK10" s="8"/>
+      <c r="AL10" s="8"/>
+      <c r="AM10" s="8"/>
+      <c r="AN10" s="8"/>
+      <c r="AO10" s="8"/>
+      <c r="AP10" s="8"/>
+      <c r="AQ10" s="8"/>
     </row>
     <row r="11" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
@@ -2227,8 +2484,12 @@
         <f>V11*$E$45</f>
         <v>1152000</v>
       </c>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
+      <c r="X11" s="65">
+        <v>2976000</v>
+      </c>
+      <c r="Y11" s="65">
+        <v>1785000</v>
+      </c>
       <c r="Z11" s="5">
         <v>1760000</v>
       </c>
@@ -2243,6 +2504,18 @@
         <f t="shared" ref="AA11:AE38" si="7">AD11*$E$45</f>
         <v>0</v>
       </c>
+      <c r="AF11" s="8"/>
+      <c r="AG11" s="8"/>
+      <c r="AH11" s="8"/>
+      <c r="AI11" s="8"/>
+      <c r="AJ11" s="8"/>
+      <c r="AK11" s="8"/>
+      <c r="AL11" s="8"/>
+      <c r="AM11" s="8"/>
+      <c r="AN11" s="8"/>
+      <c r="AO11" s="8"/>
+      <c r="AP11" s="8"/>
+      <c r="AQ11" s="8"/>
     </row>
     <row r="12" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
@@ -2333,6 +2606,18 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="AF12" s="8"/>
+      <c r="AG12" s="8"/>
+      <c r="AH12" s="8"/>
+      <c r="AI12" s="8"/>
+      <c r="AJ12" s="8"/>
+      <c r="AK12" s="8"/>
+      <c r="AL12" s="8"/>
+      <c r="AM12" s="8"/>
+      <c r="AN12" s="8"/>
+      <c r="AO12" s="8"/>
+      <c r="AP12" s="8"/>
+      <c r="AQ12" s="8"/>
     </row>
     <row r="13" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
@@ -2423,6 +2708,18 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="AF13" s="8"/>
+      <c r="AG13" s="8"/>
+      <c r="AH13" s="8"/>
+      <c r="AI13" s="8"/>
+      <c r="AJ13" s="8"/>
+      <c r="AK13" s="8"/>
+      <c r="AL13" s="8"/>
+      <c r="AM13" s="8"/>
+      <c r="AN13" s="8"/>
+      <c r="AO13" s="8"/>
+      <c r="AP13" s="8"/>
+      <c r="AQ13" s="8"/>
     </row>
     <row r="14" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B14" s="2">
@@ -2519,6 +2816,18 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="AF14" s="8"/>
+      <c r="AG14" s="8"/>
+      <c r="AH14" s="8"/>
+      <c r="AI14" s="8"/>
+      <c r="AJ14" s="8"/>
+      <c r="AK14" s="8"/>
+      <c r="AL14" s="8"/>
+      <c r="AM14" s="8"/>
+      <c r="AN14" s="8"/>
+      <c r="AO14" s="8"/>
+      <c r="AP14" s="8"/>
+      <c r="AQ14" s="8"/>
     </row>
     <row r="15" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B15" s="2">
@@ -2613,6 +2922,18 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="AF15" s="8"/>
+      <c r="AG15" s="8"/>
+      <c r="AH15" s="8"/>
+      <c r="AI15" s="8"/>
+      <c r="AJ15" s="8"/>
+      <c r="AK15" s="8"/>
+      <c r="AL15" s="8"/>
+      <c r="AM15" s="8"/>
+      <c r="AN15" s="8"/>
+      <c r="AO15" s="8"/>
+      <c r="AP15" s="8"/>
+      <c r="AQ15" s="8"/>
     </row>
     <row r="16" spans="2:46" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="2">
@@ -2670,10 +2991,10 @@
         <f t="shared" si="3"/>
         <v>840000</v>
       </c>
-      <c r="R16" s="33" t="s">
+      <c r="R16" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="S16" s="33"/>
+      <c r="S16" s="35"/>
       <c r="T16" s="5">
         <v>1740000</v>
       </c>
@@ -2705,8 +3026,20 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF16" s="8"/>
+      <c r="AG16" s="8"/>
+      <c r="AH16" s="8"/>
+      <c r="AI16" s="8"/>
+      <c r="AJ16" s="8"/>
+      <c r="AK16" s="8"/>
+      <c r="AL16" s="8"/>
+      <c r="AM16" s="8"/>
+      <c r="AN16" s="8"/>
+      <c r="AO16" s="8"/>
+      <c r="AP16" s="8"/>
+      <c r="AQ16" s="8"/>
+    </row>
+    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B17" s="2">
         <f t="shared" si="5"/>
         <v>10</v>
@@ -2793,8 +3126,20 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF17" s="8"/>
+      <c r="AG17" s="8"/>
+      <c r="AH17" s="8"/>
+      <c r="AI17" s="8"/>
+      <c r="AJ17" s="8"/>
+      <c r="AK17" s="8"/>
+      <c r="AL17" s="8"/>
+      <c r="AM17" s="8"/>
+      <c r="AN17" s="8"/>
+      <c r="AO17" s="8"/>
+      <c r="AP17" s="8"/>
+      <c r="AQ17" s="8"/>
+    </row>
+    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B18" s="2">
         <f t="shared" si="5"/>
         <v>11</v>
@@ -2886,8 +3231,20 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF18" s="8"/>
+      <c r="AG18" s="8"/>
+      <c r="AH18" s="8"/>
+      <c r="AI18" s="8"/>
+      <c r="AJ18" s="8"/>
+      <c r="AK18" s="8"/>
+      <c r="AL18" s="8"/>
+      <c r="AM18" s="8"/>
+      <c r="AN18" s="8"/>
+      <c r="AO18" s="8"/>
+      <c r="AP18" s="8"/>
+      <c r="AQ18" s="8"/>
+    </row>
+    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B19" s="2">
         <f t="shared" si="5"/>
         <v>12</v>
@@ -2981,8 +3338,20 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF19" s="8"/>
+      <c r="AG19" s="8"/>
+      <c r="AH19" s="8"/>
+      <c r="AI19" s="8"/>
+      <c r="AJ19" s="8"/>
+      <c r="AK19" s="8"/>
+      <c r="AL19" s="8"/>
+      <c r="AM19" s="8"/>
+      <c r="AN19" s="8"/>
+      <c r="AO19" s="8"/>
+      <c r="AP19" s="8"/>
+      <c r="AQ19" s="8"/>
+    </row>
+    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B20" s="2">
         <f t="shared" si="5"/>
         <v>13</v>
@@ -3072,8 +3441,20 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF20" s="26"/>
+      <c r="AG20" s="8"/>
+      <c r="AH20" s="26"/>
+      <c r="AI20" s="8"/>
+      <c r="AJ20" s="26"/>
+      <c r="AK20" s="26"/>
+      <c r="AL20" s="26"/>
+      <c r="AM20" s="26"/>
+      <c r="AN20" s="26"/>
+      <c r="AO20" s="26"/>
+      <c r="AP20" s="26"/>
+      <c r="AQ20" s="26"/>
+    </row>
+    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B21" s="2">
         <f t="shared" si="5"/>
         <v>14</v>
@@ -3163,31 +3544,52 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B22" s="2">
+      <c r="AF21" s="22">
+        <v>1828000</v>
+      </c>
+      <c r="AG21" s="23">
+        <v>497000</v>
+      </c>
+      <c r="AH21" s="22">
+        <v>1540000</v>
+      </c>
+      <c r="AI21" s="27">
+        <v>924000</v>
+      </c>
+      <c r="AJ21" s="26"/>
+      <c r="AK21" s="26"/>
+      <c r="AL21" s="26"/>
+      <c r="AM21" s="26"/>
+      <c r="AN21" s="26"/>
+      <c r="AO21" s="26"/>
+      <c r="AP21" s="26"/>
+      <c r="AQ21" s="26"/>
+    </row>
+    <row r="22" spans="1:47" s="63" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="64"/>
+      <c r="B22" s="57">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="59">
         <v>2060000</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="59">
         <v>1236000</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="59">
         <v>1630000</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="59">
         <v>978000</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="60">
         <v>1490000</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="60">
         <v>894000</v>
       </c>
       <c r="J22" s="20"/>
@@ -3195,14 +3597,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L22" s="34" t="s">
+      <c r="L22" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="M22" s="35"/>
-      <c r="N22" s="6">
+      <c r="M22" s="34"/>
+      <c r="N22" s="59">
         <v>1280000</v>
       </c>
-      <c r="O22" s="6">
+      <c r="O22" s="59">
         <v>768000</v>
       </c>
       <c r="P22" s="15"/>
@@ -3210,28 +3612,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R22" s="6">
+      <c r="R22" s="59">
         <v>1650000</v>
       </c>
-      <c r="S22" s="6">
+      <c r="S22" s="59">
         <v>990000</v>
       </c>
-      <c r="T22" s="6">
+      <c r="T22" s="59">
         <v>1700000</v>
       </c>
-      <c r="U22" s="6">
+      <c r="U22" s="59">
         <v>1020000</v>
       </c>
-      <c r="V22" s="6">
+      <c r="V22" s="59">
         <v>920000</v>
       </c>
-      <c r="W22" s="6">
+      <c r="W22" s="59">
         <v>552000</v>
       </c>
-      <c r="X22" s="7">
+      <c r="X22" s="60">
         <v>1700000</v>
       </c>
-      <c r="Y22" s="6">
+      <c r="Y22" s="59">
         <v>1020000</v>
       </c>
       <c r="Z22" s="15"/>
@@ -3239,10 +3641,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB22" s="7">
+      <c r="AB22" s="60">
         <v>1370000</v>
       </c>
-      <c r="AC22" s="6">
+      <c r="AC22" s="59">
         <v>822000</v>
       </c>
       <c r="AD22" s="15"/>
@@ -3250,8 +3652,32 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF22" s="61">
+        <v>1130000</v>
+      </c>
+      <c r="AG22" s="62">
+        <v>678000</v>
+      </c>
+      <c r="AH22" s="61">
+        <v>1725000</v>
+      </c>
+      <c r="AI22" s="61">
+        <v>1035000</v>
+      </c>
+      <c r="AJ22" s="26"/>
+      <c r="AK22" s="26"/>
+      <c r="AL22" s="26"/>
+      <c r="AM22" s="26"/>
+      <c r="AN22" s="26"/>
+      <c r="AO22" s="26"/>
+      <c r="AP22" s="26"/>
+      <c r="AQ22" s="26"/>
+      <c r="AR22" s="64"/>
+      <c r="AS22" s="64"/>
+      <c r="AT22" s="64"/>
+      <c r="AU22" s="64"/>
+    </row>
+    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B23" s="2">
         <f t="shared" si="5"/>
         <v>16</v>
@@ -3339,8 +3765,32 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF23" s="22">
+        <v>1830000</v>
+      </c>
+      <c r="AG23" s="23">
+        <v>1089000</v>
+      </c>
+      <c r="AH23" s="22">
+        <v>1960000</v>
+      </c>
+      <c r="AI23" s="27">
+        <v>1176000</v>
+      </c>
+      <c r="AJ23" s="6">
+        <v>1520000</v>
+      </c>
+      <c r="AK23" s="6">
+        <v>912000</v>
+      </c>
+      <c r="AL23" s="26"/>
+      <c r="AM23" s="26"/>
+      <c r="AN23" s="26"/>
+      <c r="AO23" s="26"/>
+      <c r="AP23" s="26"/>
+      <c r="AQ23" s="26"/>
+    </row>
+    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
         <f t="shared" si="5"/>
         <v>17</v>
@@ -3348,66 +3798,112 @@
       <c r="C24" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="5">
-        <f t="shared" ref="E24:E38" si="11">D24*$E$45</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="5">
-        <f t="shared" ref="G24:G38" si="12">F24*$E$45</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D24" s="6">
+        <v>900000</v>
+      </c>
+      <c r="E24" s="6">
+        <v>540000</v>
+      </c>
+      <c r="F24" s="28">
+        <v>2140000</v>
+      </c>
+      <c r="G24" s="27">
+        <v>1284000</v>
+      </c>
+      <c r="H24" s="7">
+        <v>1480000</v>
+      </c>
+      <c r="I24" s="7">
+        <v>888000</v>
       </c>
       <c r="J24" s="20"/>
       <c r="K24" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="L24" s="6">
+        <v>1850000</v>
+      </c>
+      <c r="M24" s="7">
+        <v>1110000</v>
+      </c>
+      <c r="N24" s="6">
+        <v>1440000</v>
+      </c>
+      <c r="O24" s="6">
+        <v>864000</v>
       </c>
       <c r="P24" s="15"/>
       <c r="Q24" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R24" s="4"/>
-      <c r="S24" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
-      <c r="V24" s="4"/>
-      <c r="W24" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X24" s="4"/>
-      <c r="Y24" s="4"/>
+      <c r="R24" s="6">
+        <v>1890000</v>
+      </c>
+      <c r="S24" s="7">
+        <v>1134000</v>
+      </c>
+      <c r="T24" s="6">
+        <v>1800000</v>
+      </c>
+      <c r="U24" s="7">
+        <v>1080000</v>
+      </c>
+      <c r="V24" s="6">
+        <v>1940000</v>
+      </c>
+      <c r="W24" s="6">
+        <v>1164000</v>
+      </c>
+      <c r="X24" s="7">
+        <v>4201000</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>2520600</v>
+      </c>
       <c r="Z24" s="15"/>
       <c r="AA24" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB24" s="7"/>
-      <c r="AC24" s="7"/>
+      <c r="AB24" s="7">
+        <v>1445000</v>
+      </c>
+      <c r="AC24" s="7">
+        <v>867000</v>
+      </c>
       <c r="AD24" s="15"/>
       <c r="AE24" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF24" s="22">
+        <v>1435000</v>
+      </c>
+      <c r="AG24" s="23">
+        <v>861000</v>
+      </c>
+      <c r="AH24" s="22">
+        <v>1725000</v>
+      </c>
+      <c r="AI24" s="27">
+        <v>1035000</v>
+      </c>
+      <c r="AJ24" s="6">
+        <v>1445000</v>
+      </c>
+      <c r="AK24" s="6">
+        <v>887000</v>
+      </c>
+      <c r="AL24" s="26"/>
+      <c r="AM24" s="26"/>
+      <c r="AN24" s="26"/>
+      <c r="AO24" s="26"/>
+      <c r="AP24" s="26"/>
+      <c r="AQ24" s="26"/>
+    </row>
+    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B25" s="2">
         <f t="shared" si="5"/>
         <v>18</v>
@@ -3415,66 +3911,112 @@
       <c r="C25" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D25" s="6">
+        <v>2140000</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1284000</v>
+      </c>
+      <c r="F25" s="28">
+        <v>1980000</v>
+      </c>
+      <c r="G25" s="27">
+        <v>1190000</v>
+      </c>
+      <c r="H25" s="7">
+        <v>2470000</v>
+      </c>
+      <c r="I25" s="7">
+        <v>1482000</v>
       </c>
       <c r="J25" s="20"/>
       <c r="K25" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="L25" s="6">
+        <v>2100000</v>
+      </c>
+      <c r="M25" s="7">
+        <v>1260000</v>
+      </c>
+      <c r="N25" s="6">
+        <v>1300000</v>
+      </c>
+      <c r="O25" s="6">
+        <v>780000</v>
       </c>
       <c r="P25" s="15"/>
       <c r="Q25" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R25" s="4"/>
-      <c r="S25" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="4"/>
-      <c r="W25" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X25" s="4"/>
-      <c r="Y25" s="4"/>
+      <c r="R25" s="6">
+        <v>2350000</v>
+      </c>
+      <c r="S25" s="7">
+        <v>1410000</v>
+      </c>
+      <c r="T25" s="6">
+        <v>1700000</v>
+      </c>
+      <c r="U25" s="7">
+        <v>1020000</v>
+      </c>
+      <c r="V25" s="6">
+        <v>2160000</v>
+      </c>
+      <c r="W25" s="6">
+        <v>1296000</v>
+      </c>
+      <c r="X25" s="7">
+        <v>3070000</v>
+      </c>
+      <c r="Y25" s="6">
+        <v>1842000</v>
+      </c>
       <c r="Z25" s="15"/>
       <c r="AA25" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB25" s="7"/>
-      <c r="AC25" s="7"/>
+      <c r="AB25" s="7">
+        <v>2095000</v>
+      </c>
+      <c r="AC25" s="7">
+        <v>1257000</v>
+      </c>
       <c r="AD25" s="15"/>
       <c r="AE25" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF25" s="22">
+        <v>1180000</v>
+      </c>
+      <c r="AG25" s="23">
+        <v>708000</v>
+      </c>
+      <c r="AH25" s="22">
+        <v>9245000</v>
+      </c>
+      <c r="AI25" s="27">
+        <v>5547000</v>
+      </c>
+      <c r="AJ25" s="6">
+        <v>1975000</v>
+      </c>
+      <c r="AK25" s="6">
+        <v>1185000</v>
+      </c>
+      <c r="AL25" s="26"/>
+      <c r="AM25" s="26"/>
+      <c r="AN25" s="26"/>
+      <c r="AO25" s="26"/>
+      <c r="AP25" s="26"/>
+      <c r="AQ25" s="26"/>
+    </row>
+    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B26" s="2">
         <f t="shared" si="5"/>
         <v>19</v>
@@ -3482,66 +4024,112 @@
       <c r="C26" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D26" s="6">
+        <v>1800000</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1080000</v>
+      </c>
+      <c r="F26" s="28">
+        <v>1860000</v>
+      </c>
+      <c r="G26" s="27">
+        <v>1116000</v>
+      </c>
+      <c r="H26" s="7">
+        <v>1205000</v>
+      </c>
+      <c r="I26" s="7">
+        <v>723000</v>
       </c>
       <c r="J26" s="20"/>
       <c r="K26" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="L26" s="6">
+        <v>1600000</v>
+      </c>
+      <c r="M26" s="7">
+        <v>960000</v>
+      </c>
+      <c r="N26" s="6">
+        <v>1588000</v>
+      </c>
+      <c r="O26" s="6">
+        <v>952000</v>
       </c>
       <c r="P26" s="15"/>
       <c r="Q26" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R26" s="4"/>
-      <c r="S26" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
-      <c r="V26" s="4"/>
-      <c r="W26" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="4"/>
-      <c r="Y26" s="4"/>
+      <c r="R26" s="6">
+        <v>1600000</v>
+      </c>
+      <c r="S26" s="7">
+        <v>960000</v>
+      </c>
+      <c r="T26" s="6">
+        <v>1760000</v>
+      </c>
+      <c r="U26" s="7">
+        <v>1056000</v>
+      </c>
+      <c r="V26" s="6">
+        <v>1650000</v>
+      </c>
+      <c r="W26" s="6">
+        <v>990000</v>
+      </c>
+      <c r="X26" s="7">
+        <v>3890000</v>
+      </c>
+      <c r="Y26" s="6">
+        <v>2334000</v>
+      </c>
       <c r="Z26" s="15"/>
       <c r="AA26" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB26" s="7"/>
-      <c r="AC26" s="7"/>
+      <c r="AB26" s="7">
+        <v>1750000</v>
+      </c>
+      <c r="AC26" s="7">
+        <v>1050000</v>
+      </c>
       <c r="AD26" s="15"/>
       <c r="AE26" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF26" s="22">
+        <v>1750000</v>
+      </c>
+      <c r="AG26" s="23">
+        <v>1050000</v>
+      </c>
+      <c r="AH26" s="22">
+        <v>1740000</v>
+      </c>
+      <c r="AI26" s="27">
+        <v>1044000</v>
+      </c>
+      <c r="AJ26" s="6">
+        <v>1850000</v>
+      </c>
+      <c r="AK26" s="6">
+        <v>1110000</v>
+      </c>
+      <c r="AL26" s="26"/>
+      <c r="AM26" s="26"/>
+      <c r="AN26" s="26"/>
+      <c r="AO26" s="26"/>
+      <c r="AP26" s="26"/>
+      <c r="AQ26" s="26"/>
+    </row>
+    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B27" s="2">
         <f t="shared" si="5"/>
         <v>20</v>
@@ -3549,66 +4137,110 @@
       <c r="C27" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D27" s="6">
+        <v>2279000</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1360000</v>
+      </c>
+      <c r="F27" s="28">
+        <v>2220000</v>
+      </c>
+      <c r="G27" s="27">
+        <v>1332000</v>
+      </c>
+      <c r="H27" s="7">
+        <v>720000</v>
+      </c>
+      <c r="I27" s="7">
+        <v>720000</v>
       </c>
       <c r="J27" s="20"/>
       <c r="K27" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="L27" s="6">
+        <v>1300000</v>
+      </c>
+      <c r="M27" s="7">
+        <v>780000</v>
+      </c>
+      <c r="N27" s="6">
+        <v>1240000</v>
+      </c>
+      <c r="O27" s="6">
+        <v>744000</v>
       </c>
       <c r="P27" s="15"/>
       <c r="Q27" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R27" s="4"/>
-      <c r="S27" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
-      <c r="V27" s="4"/>
-      <c r="W27" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X27" s="4"/>
-      <c r="Y27" s="4"/>
+      <c r="R27" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="S27" s="45"/>
+      <c r="T27" s="6">
+        <v>1810000</v>
+      </c>
+      <c r="U27" s="7">
+        <v>1086000</v>
+      </c>
+      <c r="V27" s="6">
+        <v>1400000</v>
+      </c>
+      <c r="W27" s="6">
+        <v>840000</v>
+      </c>
+      <c r="X27" s="7">
+        <v>4064000</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>2438400</v>
+      </c>
       <c r="Z27" s="15"/>
       <c r="AA27" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB27" s="7"/>
-      <c r="AC27" s="7"/>
+      <c r="AB27" s="7">
+        <v>1370000</v>
+      </c>
+      <c r="AC27" s="7">
+        <v>822000</v>
+      </c>
       <c r="AD27" s="15"/>
       <c r="AE27" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF27" s="22">
+        <v>1185000</v>
+      </c>
+      <c r="AG27" s="23">
+        <v>715000</v>
+      </c>
+      <c r="AH27" s="22">
+        <v>910000</v>
+      </c>
+      <c r="AI27" s="27">
+        <v>546000</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>670000</v>
+      </c>
+      <c r="AK27" s="6">
+        <v>402000</v>
+      </c>
+      <c r="AL27" s="26"/>
+      <c r="AM27" s="26"/>
+      <c r="AN27" s="26"/>
+      <c r="AO27" s="26"/>
+      <c r="AP27" s="26"/>
+      <c r="AQ27" s="26"/>
+    </row>
+    <row r="28" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B28" s="2">
         <f t="shared" si="5"/>
         <v>21</v>
@@ -3616,66 +4248,110 @@
       <c r="C28" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D28" s="6">
+        <v>1500000</v>
+      </c>
+      <c r="E28" s="6">
+        <v>900000</v>
+      </c>
+      <c r="F28" s="28">
+        <v>3270000</v>
+      </c>
+      <c r="G28" s="27">
+        <v>1962000</v>
+      </c>
+      <c r="H28" s="7">
+        <v>1450000</v>
+      </c>
+      <c r="I28" s="7">
+        <v>870000</v>
       </c>
       <c r="J28" s="20"/>
       <c r="K28" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="L28" s="6">
+        <v>1360000</v>
+      </c>
+      <c r="M28" s="7">
+        <v>816000</v>
+      </c>
+      <c r="N28" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="O28" s="47"/>
       <c r="P28" s="15"/>
       <c r="Q28" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R28" s="4"/>
-      <c r="S28" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
-      <c r="V28" s="4"/>
-      <c r="W28" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X28" s="4"/>
-      <c r="Y28" s="4"/>
+      <c r="R28" s="6">
+        <v>1450000</v>
+      </c>
+      <c r="S28" s="7">
+        <v>870000</v>
+      </c>
+      <c r="T28" s="6">
+        <v>1800000</v>
+      </c>
+      <c r="U28" s="7">
+        <v>1080000</v>
+      </c>
+      <c r="V28" s="6">
+        <v>1880000</v>
+      </c>
+      <c r="W28" s="6">
+        <v>1128000</v>
+      </c>
+      <c r="X28" s="7">
+        <v>3150000</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>1890000</v>
+      </c>
       <c r="Z28" s="15"/>
       <c r="AA28" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB28" s="7"/>
-      <c r="AC28" s="7"/>
+      <c r="AB28" s="7">
+        <v>1440000</v>
+      </c>
+      <c r="AC28" s="7">
+        <v>864000</v>
+      </c>
       <c r="AD28" s="15"/>
       <c r="AE28" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF28" s="22">
+        <v>1330000</v>
+      </c>
+      <c r="AG28" s="23">
+        <v>798000</v>
+      </c>
+      <c r="AH28" s="22">
+        <v>650000</v>
+      </c>
+      <c r="AI28" s="27">
+        <v>390000</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>3570000</v>
+      </c>
+      <c r="AK28" s="6">
+        <v>2142000</v>
+      </c>
+      <c r="AL28" s="26"/>
+      <c r="AM28" s="26"/>
+      <c r="AN28" s="26"/>
+      <c r="AO28" s="26"/>
+      <c r="AP28" s="26"/>
+      <c r="AQ28" s="26"/>
+    </row>
+    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B29" s="2">
         <f t="shared" si="5"/>
         <v>22</v>
@@ -3683,66 +4359,108 @@
       <c r="C29" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D29" s="6">
+        <v>1410000</v>
+      </c>
+      <c r="E29" s="6">
+        <v>846000</v>
+      </c>
+      <c r="F29" s="28">
+        <v>1355000</v>
+      </c>
+      <c r="G29" s="27">
+        <v>813000</v>
+      </c>
+      <c r="H29" s="7">
+        <v>1855000</v>
+      </c>
+      <c r="I29" s="7">
+        <v>1113000</v>
       </c>
       <c r="J29" s="20"/>
       <c r="K29" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="L29" s="6">
+        <v>1670000</v>
+      </c>
+      <c r="M29" s="7">
+        <v>1002000</v>
+      </c>
+      <c r="N29" s="48"/>
+      <c r="O29" s="49"/>
       <c r="P29" s="15"/>
       <c r="Q29" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R29" s="4"/>
-      <c r="S29" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
-      <c r="V29" s="4"/>
-      <c r="W29" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X29" s="4"/>
-      <c r="Y29" s="4"/>
+      <c r="R29" s="6">
+        <v>1560000</v>
+      </c>
+      <c r="S29" s="7">
+        <v>936000</v>
+      </c>
+      <c r="T29" s="6">
+        <v>930000</v>
+      </c>
+      <c r="U29" s="7">
+        <v>558000</v>
+      </c>
+      <c r="V29" s="6">
+        <v>1990000</v>
+      </c>
+      <c r="W29" s="6">
+        <v>1200000</v>
+      </c>
+      <c r="X29" s="7">
+        <v>3850000</v>
+      </c>
+      <c r="Y29" s="6">
+        <v>2310000</v>
+      </c>
       <c r="Z29" s="15"/>
       <c r="AA29" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB29" s="7"/>
-      <c r="AC29" s="7"/>
+      <c r="AB29" s="7">
+        <v>2952000</v>
+      </c>
+      <c r="AC29" s="7">
+        <v>1771000</v>
+      </c>
       <c r="AD29" s="15"/>
       <c r="AE29" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF29" s="22">
+        <v>1100000</v>
+      </c>
+      <c r="AG29" s="23">
+        <v>660000</v>
+      </c>
+      <c r="AH29" s="22">
+        <v>510000</v>
+      </c>
+      <c r="AI29" s="27">
+        <v>306000</v>
+      </c>
+      <c r="AJ29" s="6">
+        <v>1380000</v>
+      </c>
+      <c r="AK29" s="6">
+        <v>828000</v>
+      </c>
+      <c r="AL29" s="26"/>
+      <c r="AM29" s="26"/>
+      <c r="AN29" s="26"/>
+      <c r="AO29" s="26"/>
+      <c r="AP29" s="26"/>
+      <c r="AQ29" s="26"/>
+    </row>
+    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B30" s="2">
         <f t="shared" si="5"/>
         <v>23</v>
@@ -3750,66 +4468,104 @@
       <c r="C30" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D30" s="6">
+        <v>1530000</v>
+      </c>
+      <c r="E30" s="6">
+        <v>918000</v>
+      </c>
+      <c r="F30" s="28">
+        <v>1130000</v>
+      </c>
+      <c r="G30" s="27">
+        <v>678000</v>
+      </c>
+      <c r="H30" s="7">
+        <v>1370000</v>
+      </c>
+      <c r="I30" s="7">
+        <v>822000</v>
       </c>
       <c r="J30" s="20"/>
       <c r="K30" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="L30" s="6">
+        <v>2550000</v>
+      </c>
+      <c r="M30" s="7">
+        <v>1530000</v>
+      </c>
+      <c r="N30" s="48"/>
+      <c r="O30" s="49"/>
       <c r="P30" s="15"/>
       <c r="Q30" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R30" s="4"/>
-      <c r="S30" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="4"/>
-      <c r="W30" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="4"/>
+      <c r="R30" s="6">
+        <v>1210000</v>
+      </c>
+      <c r="S30" s="7">
+        <v>726000</v>
+      </c>
+      <c r="T30" s="6">
+        <v>780000</v>
+      </c>
+      <c r="U30" s="7">
+        <v>468000</v>
+      </c>
+      <c r="V30" s="6">
+        <v>1980000</v>
+      </c>
+      <c r="W30" s="6">
+        <v>1200000</v>
+      </c>
+      <c r="X30" s="7">
+        <v>3585000</v>
+      </c>
+      <c r="Y30" s="6">
+        <v>2151000</v>
+      </c>
       <c r="Z30" s="15"/>
       <c r="AA30" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB30" s="7"/>
-      <c r="AC30" s="7"/>
+      <c r="AB30" s="7">
+        <v>1810000</v>
+      </c>
+      <c r="AC30" s="7">
+        <v>1086000</v>
+      </c>
       <c r="AD30" s="15"/>
       <c r="AE30" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF30" s="46" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG30" s="47"/>
+      <c r="AH30" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI30" s="47"/>
+      <c r="AJ30" s="6">
+        <v>1560000</v>
+      </c>
+      <c r="AK30" s="6">
+        <v>936000</v>
+      </c>
+      <c r="AL30" s="26"/>
+      <c r="AM30" s="26"/>
+      <c r="AN30" s="26"/>
+      <c r="AO30" s="26"/>
+      <c r="AP30" s="26"/>
+      <c r="AQ30" s="26"/>
+    </row>
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B31" s="2">
         <f t="shared" si="5"/>
         <v>24</v>
@@ -3817,66 +4573,100 @@
       <c r="C31" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D31" s="6">
+        <v>2190000</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1095000</v>
+      </c>
+      <c r="F31" s="28">
+        <v>1730000</v>
+      </c>
+      <c r="G31" s="27">
+        <v>865000</v>
+      </c>
+      <c r="H31" s="7">
+        <v>1500000</v>
+      </c>
+      <c r="I31" s="7">
+        <v>900000</v>
       </c>
       <c r="J31" s="20"/>
       <c r="K31" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="L31" s="6">
+        <v>1760000</v>
+      </c>
+      <c r="M31" s="7">
+        <v>880000</v>
+      </c>
+      <c r="N31" s="48"/>
+      <c r="O31" s="49"/>
       <c r="P31" s="15"/>
       <c r="Q31" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R31" s="4"/>
-      <c r="S31" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
+      <c r="R31" s="6">
+        <v>2440000</v>
+      </c>
+      <c r="S31" s="7">
+        <v>1220000</v>
+      </c>
+      <c r="T31" s="6">
+        <v>300000</v>
+      </c>
+      <c r="U31" s="7">
+        <v>300000</v>
+      </c>
+      <c r="V31" s="6">
+        <v>2370000</v>
+      </c>
+      <c r="W31" s="6">
+        <v>1190000</v>
+      </c>
+      <c r="X31" s="7">
+        <v>3600000</v>
+      </c>
+      <c r="Y31" s="6">
+        <v>1800000</v>
+      </c>
       <c r="Z31" s="15"/>
       <c r="AA31" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB31" s="7"/>
-      <c r="AC31" s="7"/>
+      <c r="AB31" s="7">
+        <v>1810000</v>
+      </c>
+      <c r="AC31" s="7">
+        <v>905000</v>
+      </c>
       <c r="AD31" s="15"/>
       <c r="AE31" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF31" s="48"/>
+      <c r="AG31" s="49"/>
+      <c r="AH31" s="48"/>
+      <c r="AI31" s="49"/>
+      <c r="AJ31" s="6">
+        <v>2010000</v>
+      </c>
+      <c r="AK31" s="6">
+        <v>1005000</v>
+      </c>
+      <c r="AL31" s="26"/>
+      <c r="AM31" s="26"/>
+      <c r="AN31" s="26"/>
+      <c r="AO31" s="26"/>
+      <c r="AP31" s="26"/>
+      <c r="AQ31" s="26"/>
+    </row>
+    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B32" s="2">
         <f t="shared" si="5"/>
         <v>25</v>
@@ -3884,66 +4674,96 @@
       <c r="C32" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D32" s="6">
+        <v>2440000</v>
+      </c>
+      <c r="E32" s="6">
+        <v>1220000</v>
+      </c>
+      <c r="F32" s="28">
+        <v>1975000</v>
+      </c>
+      <c r="G32" s="27">
+        <v>988000</v>
+      </c>
+      <c r="H32" s="7">
+        <v>1860000</v>
+      </c>
+      <c r="I32" s="7">
+        <v>930000</v>
       </c>
       <c r="J32" s="20"/>
       <c r="K32" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="L32" s="6">
+        <v>1850000</v>
+      </c>
+      <c r="M32" s="7">
+        <v>925000</v>
+      </c>
+      <c r="N32" s="48"/>
+      <c r="O32" s="49"/>
       <c r="P32" s="15"/>
       <c r="Q32" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R32" s="4"/>
-      <c r="S32" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
-      <c r="W32" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="4"/>
+      <c r="R32" s="6">
+        <v>1850000</v>
+      </c>
+      <c r="S32" s="7">
+        <v>925000</v>
+      </c>
+      <c r="T32" s="15"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="6">
+        <v>900000</v>
+      </c>
+      <c r="W32" s="6">
+        <v>540000</v>
+      </c>
+      <c r="X32" s="7">
+        <v>4400000</v>
+      </c>
+      <c r="Y32" s="6">
+        <v>2200000</v>
+      </c>
       <c r="Z32" s="15"/>
       <c r="AA32" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB32" s="7"/>
-      <c r="AC32" s="7"/>
+      <c r="AB32" s="7">
+        <v>1710000</v>
+      </c>
+      <c r="AC32" s="7">
+        <v>855000</v>
+      </c>
       <c r="AD32" s="15"/>
       <c r="AE32" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF32" s="48"/>
+      <c r="AG32" s="49"/>
+      <c r="AH32" s="48"/>
+      <c r="AI32" s="49"/>
+      <c r="AJ32" s="6">
+        <v>2370000</v>
+      </c>
+      <c r="AK32" s="6">
+        <v>1185000</v>
+      </c>
+      <c r="AL32" s="26"/>
+      <c r="AM32" s="26"/>
+      <c r="AN32" s="26"/>
+      <c r="AO32" s="26"/>
+      <c r="AP32" s="26"/>
+      <c r="AQ32" s="26"/>
+    </row>
+    <row r="33" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B33" s="2">
         <f t="shared" si="5"/>
         <v>26</v>
@@ -3951,66 +4771,96 @@
       <c r="C33" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D33" s="6">
+        <v>2050000</v>
+      </c>
+      <c r="E33" s="6">
+        <v>1025000</v>
+      </c>
+      <c r="F33" s="28">
+        <v>2280000</v>
+      </c>
+      <c r="G33" s="27">
+        <v>1140000</v>
+      </c>
+      <c r="H33" s="7">
+        <v>1270000</v>
+      </c>
+      <c r="I33" s="7">
+        <v>762000</v>
       </c>
       <c r="J33" s="20"/>
       <c r="K33" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="L33" s="6">
+        <v>1180000</v>
+      </c>
+      <c r="M33" s="7">
+        <v>708000</v>
+      </c>
+      <c r="N33" s="48"/>
+      <c r="O33" s="49"/>
       <c r="P33" s="15"/>
       <c r="Q33" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R33" s="4"/>
-      <c r="S33" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="4"/>
-      <c r="W33" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="4"/>
+      <c r="R33" s="6">
+        <v>2100000</v>
+      </c>
+      <c r="S33" s="7">
+        <v>1050000</v>
+      </c>
+      <c r="T33" s="15"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="6">
+        <v>2570000</v>
+      </c>
+      <c r="W33" s="6">
+        <v>1300000</v>
+      </c>
+      <c r="X33" s="7">
+        <v>2650000</v>
+      </c>
+      <c r="Y33" s="6">
+        <v>1325000</v>
+      </c>
       <c r="Z33" s="15"/>
       <c r="AA33" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB33" s="7"/>
-      <c r="AC33" s="7"/>
+      <c r="AB33" s="7">
+        <v>2060000</v>
+      </c>
+      <c r="AC33" s="7">
+        <v>1030000</v>
+      </c>
       <c r="AD33" s="15"/>
       <c r="AE33" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF33" s="48"/>
+      <c r="AG33" s="49"/>
+      <c r="AH33" s="48"/>
+      <c r="AI33" s="49"/>
+      <c r="AJ33" s="6">
+        <v>2000000</v>
+      </c>
+      <c r="AK33" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="AL33" s="26"/>
+      <c r="AM33" s="26"/>
+      <c r="AN33" s="26"/>
+      <c r="AO33" s="26"/>
+      <c r="AP33" s="26"/>
+      <c r="AQ33" s="26"/>
+    </row>
+    <row r="34" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B34" s="2">
         <f t="shared" si="5"/>
         <v>27</v>
@@ -4018,66 +4868,96 @@
       <c r="C34" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="4"/>
-      <c r="I34" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D34" s="6">
+        <v>2530000</v>
+      </c>
+      <c r="E34" s="6">
+        <v>1265000</v>
+      </c>
+      <c r="F34" s="52">
+        <v>2190000</v>
+      </c>
+      <c r="G34" s="27">
+        <v>1095000</v>
+      </c>
+      <c r="H34" s="7">
+        <v>1410000</v>
+      </c>
+      <c r="I34" s="7">
+        <v>846000</v>
       </c>
       <c r="J34" s="20"/>
       <c r="K34" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="L34" s="6">
+        <v>1280000</v>
+      </c>
+      <c r="M34" s="7">
+        <v>768000</v>
+      </c>
+      <c r="N34" s="48"/>
+      <c r="O34" s="49"/>
       <c r="P34" s="15"/>
       <c r="Q34" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R34" s="4"/>
-      <c r="S34" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="4"/>
-      <c r="W34" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X34" s="4"/>
-      <c r="Y34" s="4"/>
+      <c r="R34" s="6">
+        <v>1155000</v>
+      </c>
+      <c r="S34" s="7">
+        <v>693000</v>
+      </c>
+      <c r="T34" s="15"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="6">
+        <v>1700000</v>
+      </c>
+      <c r="W34" s="6">
+        <v>850000</v>
+      </c>
+      <c r="X34" s="7">
+        <v>590000</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>354000</v>
+      </c>
       <c r="Z34" s="15"/>
       <c r="AA34" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB34" s="7"/>
-      <c r="AC34" s="7"/>
+      <c r="AB34" s="7">
+        <v>2080000</v>
+      </c>
+      <c r="AC34" s="7">
+        <v>1040000</v>
+      </c>
       <c r="AD34" s="15"/>
       <c r="AE34" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF34" s="50"/>
+      <c r="AG34" s="51"/>
+      <c r="AH34" s="48"/>
+      <c r="AI34" s="49"/>
+      <c r="AJ34" s="6">
+        <v>2100000</v>
+      </c>
+      <c r="AK34" s="6">
+        <v>1050000</v>
+      </c>
+      <c r="AL34" s="26"/>
+      <c r="AM34" s="26"/>
+      <c r="AN34" s="26"/>
+      <c r="AO34" s="26"/>
+      <c r="AP34" s="26"/>
+      <c r="AQ34" s="26"/>
+    </row>
+    <row r="35" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B35" s="2">
         <f t="shared" si="5"/>
         <v>28</v>
@@ -4085,66 +4965,98 @@
       <c r="C35" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="4"/>
-      <c r="I35" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D35" s="6">
+        <v>1300000</v>
+      </c>
+      <c r="E35" s="6">
+        <v>780000</v>
+      </c>
+      <c r="F35" s="52">
+        <v>1710000</v>
+      </c>
+      <c r="G35" s="27">
+        <v>855000</v>
+      </c>
+      <c r="H35" s="7">
+        <v>1050000</v>
+      </c>
+      <c r="I35" s="7">
+        <v>630000</v>
       </c>
       <c r="J35" s="20"/>
       <c r="K35" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="L35" s="6">
+        <v>1410000</v>
+      </c>
+      <c r="M35" s="7">
+        <v>846000</v>
+      </c>
+      <c r="N35" s="48"/>
+      <c r="O35" s="49"/>
       <c r="P35" s="15"/>
       <c r="Q35" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R35" s="4"/>
-      <c r="S35" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
+      <c r="R35" s="6">
+        <v>850000</v>
+      </c>
+      <c r="S35" s="7">
+        <v>510000</v>
+      </c>
+      <c r="T35" s="15"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="6">
+        <v>1490000</v>
+      </c>
+      <c r="W35" s="6">
+        <v>890000</v>
+      </c>
+      <c r="X35" s="7">
+        <v>2500000</v>
+      </c>
+      <c r="Y35" s="6">
+        <v>1250000</v>
+      </c>
       <c r="Z35" s="15"/>
       <c r="AA35" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB35" s="7"/>
-      <c r="AC35" s="7"/>
+      <c r="AB35" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC35" s="54"/>
       <c r="AD35" s="15"/>
       <c r="AE35" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF35" s="27">
+        <v>1050000</v>
+      </c>
+      <c r="AG35" s="23">
+        <v>525000</v>
+      </c>
+      <c r="AH35" s="48"/>
+      <c r="AI35" s="49"/>
+      <c r="AJ35" s="6">
+        <v>3435000</v>
+      </c>
+      <c r="AK35" s="6">
+        <v>1717000</v>
+      </c>
+      <c r="AL35" s="26"/>
+      <c r="AM35" s="26"/>
+      <c r="AN35" s="26"/>
+      <c r="AO35" s="26"/>
+      <c r="AP35" s="26"/>
+      <c r="AQ35" s="26"/>
+    </row>
+    <row r="36" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B36" s="2">
         <f t="shared" si="5"/>
         <v>29</v>
@@ -4152,135 +5064,215 @@
       <c r="C36" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="4"/>
-      <c r="I36" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D36" s="6">
+        <v>2230000</v>
+      </c>
+      <c r="E36" s="6">
+        <v>1110000</v>
+      </c>
+      <c r="F36" s="52">
+        <v>1730000</v>
+      </c>
+      <c r="G36" s="27">
+        <v>865000</v>
+      </c>
+      <c r="H36" s="7">
+        <v>1967000</v>
+      </c>
+      <c r="I36" s="7">
+        <v>984000</v>
       </c>
       <c r="J36" s="20"/>
       <c r="K36" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="L36" s="6">
+        <v>1980000</v>
+      </c>
+      <c r="M36" s="7">
+        <v>990000</v>
+      </c>
+      <c r="N36" s="48"/>
+      <c r="O36" s="49"/>
       <c r="P36" s="15"/>
       <c r="Q36" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R36" s="4"/>
-      <c r="S36" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
+      <c r="R36" s="6">
+        <v>1700000</v>
+      </c>
+      <c r="S36" s="7">
+        <v>850000</v>
+      </c>
+      <c r="T36" s="15"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="6">
+        <v>1710000</v>
+      </c>
+      <c r="W36" s="6">
+        <v>860000</v>
+      </c>
+      <c r="X36" s="7">
+        <v>2415000</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1207000</v>
+      </c>
       <c r="Z36" s="15"/>
       <c r="AA36" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB36" s="7"/>
-      <c r="AC36" s="7"/>
+      <c r="AB36" s="7">
+        <v>1150000</v>
+      </c>
+      <c r="AC36" s="7">
+        <v>690000</v>
+      </c>
       <c r="AD36" s="15"/>
       <c r="AE36" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF36" s="27">
+        <v>1760000</v>
+      </c>
+      <c r="AG36" s="23">
+        <v>880000</v>
+      </c>
+      <c r="AH36" s="48"/>
+      <c r="AI36" s="49"/>
+      <c r="AJ36" s="27">
+        <v>1840000</v>
+      </c>
+      <c r="AK36" s="27">
+        <v>920000</v>
+      </c>
+      <c r="AL36" s="7">
+        <v>90000</v>
+      </c>
+      <c r="AM36" s="7">
+        <v>54000</v>
+      </c>
+      <c r="AN36" s="26"/>
+      <c r="AO36" s="26"/>
+      <c r="AP36" s="26"/>
+      <c r="AQ36" s="26"/>
+    </row>
+    <row r="37" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B37" s="2">
-        <f t="shared" ref="B37:B38" si="13">B36+1</f>
+        <f t="shared" ref="B37:B38" si="11">B36+1</f>
         <v>30</v>
       </c>
       <c r="C37" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="5">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="5">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="4"/>
-      <c r="I37" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D37" s="6">
+        <v>1720000</v>
+      </c>
+      <c r="E37" s="6">
+        <v>860000</v>
+      </c>
+      <c r="F37" s="52">
+        <v>1140000</v>
+      </c>
+      <c r="G37" s="27">
+        <v>684000</v>
+      </c>
+      <c r="H37" s="7">
+        <v>2380000</v>
+      </c>
+      <c r="I37" s="7">
+        <v>1190000</v>
       </c>
       <c r="J37" s="20"/>
       <c r="K37" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="L37" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="M37" s="56"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="49"/>
       <c r="P37" s="15"/>
       <c r="Q37" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R37" s="4"/>
-      <c r="S37" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="4"/>
-      <c r="W37" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X37" s="4"/>
-      <c r="Y37" s="4"/>
+      <c r="R37" s="6">
+        <v>3497000</v>
+      </c>
+      <c r="S37" s="7">
+        <v>1749000</v>
+      </c>
+      <c r="T37" s="15"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="6">
+        <v>1750000</v>
+      </c>
+      <c r="W37" s="6">
+        <v>860000</v>
+      </c>
+      <c r="X37" s="7">
+        <v>3000000</v>
+      </c>
+      <c r="Y37" s="6">
+        <v>1500000</v>
+      </c>
       <c r="Z37" s="15"/>
       <c r="AA37" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB37" s="7"/>
-      <c r="AC37" s="7"/>
+      <c r="AB37" s="7">
+        <v>2060000</v>
+      </c>
+      <c r="AC37" s="7">
+        <v>1030000</v>
+      </c>
       <c r="AD37" s="15"/>
       <c r="AE37" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF37" s="27">
+        <v>1730000</v>
+      </c>
+      <c r="AG37" s="23">
+        <v>865000</v>
+      </c>
+      <c r="AH37" s="48"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="27">
+        <v>3815000</v>
+      </c>
+      <c r="AK37" s="27">
+        <v>1900000</v>
+      </c>
+      <c r="AL37" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="AM37" s="54"/>
+      <c r="AN37" s="6">
+        <v>380000</v>
+      </c>
+      <c r="AO37" s="7">
+        <v>228000</v>
+      </c>
+      <c r="AP37" s="6">
+        <v>660000</v>
+      </c>
+      <c r="AQ37" s="6">
+        <v>396000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B38" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="C38" s="11" t="s">
@@ -4288,12 +5280,12 @@
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="E24:E38" si="12">D38*$E$45</f>
         <v>0</v>
       </c>
       <c r="F38" s="4"/>
       <c r="G38" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="G24:G38" si="13">F38*$E$45</f>
         <v>0</v>
       </c>
       <c r="H38" s="4"/>
@@ -4308,11 +5300,8 @@
       </c>
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="N38" s="50"/>
+      <c r="O38" s="51"/>
       <c r="P38" s="15"/>
       <c r="Q38" s="14">
         <f t="shared" si="3"/>
@@ -4323,8 +5312,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
+      <c r="T38" s="15"/>
+      <c r="U38" s="15"/>
       <c r="V38" s="4"/>
       <c r="W38" s="5">
         <f t="shared" si="10"/>
@@ -4344,8 +5333,35 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="AF38" s="21"/>
+      <c r="AG38" s="7">
+        <f t="shared" ref="AG24:AG38" si="14">AF38*$E$45</f>
+        <v>0</v>
+      </c>
+      <c r="AH38" s="50"/>
+      <c r="AI38" s="51"/>
+      <c r="AJ38" s="21"/>
+      <c r="AK38" s="7">
+        <f t="shared" ref="AK24:AK38" si="15">AJ38*$E$45</f>
+        <v>0</v>
+      </c>
+      <c r="AL38" s="21"/>
+      <c r="AM38" s="7">
+        <f t="shared" ref="AM36:AM38" si="16">AL38*$E$45</f>
+        <v>0</v>
+      </c>
+      <c r="AN38" s="21"/>
+      <c r="AO38" s="7">
+        <f t="shared" ref="AO36:AO38" si="17">AN38*$E$45</f>
+        <v>0</v>
+      </c>
+      <c r="AP38" s="21"/>
+      <c r="AQ38" s="7">
+        <f t="shared" ref="AQ38" si="18">AP38*$E$45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:43" x14ac:dyDescent="0.25">
       <c r="D45" t="s">
         <v>23</v>
       </c>
@@ -4354,14 +5370,20 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="17">
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
+  <mergeCells count="30">
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="AP6:AQ6"/>
+    <mergeCell ref="AL37:AM37"/>
+    <mergeCell ref="AL6:AM6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB35:AC35"/>
+    <mergeCell ref="AF30:AG34"/>
+    <mergeCell ref="AH30:AI38"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="N28:O38"/>
+    <mergeCell ref="AF6:AG6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AJ6:AK6"/>
     <mergeCell ref="Z6:AA6"/>
     <mergeCell ref="AD6:AE6"/>
     <mergeCell ref="R16:S16"/>
@@ -4373,6 +5395,12 @@
     <mergeCell ref="T6:U6"/>
     <mergeCell ref="V6:W6"/>
     <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Chấm công/CHẤM CÔNG T1 2026.xlsx
+++ b/Chấm công/CHẤM CÔNG T1 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Duc Anh\Chấm công\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A57B94-64DD-4645-8034-D973B567BCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B4000D-47E8-44EB-9B00-7C1FA27F88FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="487" activeTab="1" xr2:uid="{5BB9A907-C889-48BA-A08B-CDCC7DB0058E}"/>
   </bookViews>
@@ -205,7 +205,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="13"/>
       <color theme="1"/>
@@ -280,6 +280,12 @@
     <font>
       <sz val="13"/>
       <color rgb="FFFFFF00"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -498,7 +504,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -576,6 +582,32 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="4" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -588,14 +620,50 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -621,66 +689,19 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="4" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -741,40 +762,42 @@
       <sheetName val="28-01"/>
       <sheetName val="29-01"/>
       <sheetName val="30-01"/>
+      <sheetName val="31-01"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
       <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="29" refreshError="1"/>
+      <sheetData sheetId="30" refreshError="1"/>
+      <sheetData sheetId="31" refreshError="1"/>
+      <sheetData sheetId="32" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1136,22 +1159,22 @@
     </row>
     <row r="5" spans="2:22" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:22" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="29" t="s">
+      <c r="C6" s="42"/>
+      <c r="D6" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="29" t="s">
+      <c r="E6" s="40"/>
+      <c r="F6" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="29" t="s">
+      <c r="G6" s="40"/>
+      <c r="H6" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="30"/>
+      <c r="I6" s="40"/>
       <c r="V6" t="s">
         <v>33</v>
       </c>
@@ -1903,90 +1926,90 @@
     </row>
     <row r="5" spans="2:46" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:46" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="29" t="s">
+      <c r="C6" s="42"/>
+      <c r="D6" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="29" t="s">
+      <c r="E6" s="40"/>
+      <c r="F6" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="29" t="s">
+      <c r="G6" s="40"/>
+      <c r="H6" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="30"/>
-      <c r="J6" s="29" t="s">
+      <c r="I6" s="40"/>
+      <c r="J6" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="K6" s="30"/>
-      <c r="L6" s="29" t="s">
+      <c r="K6" s="40"/>
+      <c r="L6" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="M6" s="30"/>
-      <c r="N6" s="29" t="s">
+      <c r="M6" s="40"/>
+      <c r="N6" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="O6" s="30"/>
-      <c r="P6" s="29" t="s">
+      <c r="O6" s="40"/>
+      <c r="P6" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="29" t="s">
+      <c r="Q6" s="40"/>
+      <c r="R6" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="S6" s="30"/>
-      <c r="T6" s="29" t="s">
+      <c r="S6" s="40"/>
+      <c r="T6" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="U6" s="30"/>
-      <c r="V6" s="29" t="s">
+      <c r="U6" s="40"/>
+      <c r="V6" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="W6" s="30"/>
-      <c r="X6" s="29" t="s">
+      <c r="W6" s="40"/>
+      <c r="X6" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="Y6" s="30"/>
-      <c r="Z6" s="29" t="s">
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="29" t="s">
+      <c r="AA6" s="40"/>
+      <c r="AB6" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="AC6" s="30"/>
-      <c r="AD6" s="29" t="s">
+      <c r="AC6" s="40"/>
+      <c r="AD6" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="AE6" s="30"/>
-      <c r="AF6" s="29" t="s">
+      <c r="AE6" s="40"/>
+      <c r="AF6" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="AG6" s="30"/>
-      <c r="AH6" s="29" t="s">
+      <c r="AG6" s="40"/>
+      <c r="AH6" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="29" t="s">
+      <c r="AI6" s="40"/>
+      <c r="AJ6" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="AK6" s="30"/>
-      <c r="AL6" s="29" t="s">
+      <c r="AK6" s="40"/>
+      <c r="AL6" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="AM6" s="30"/>
-      <c r="AN6" s="29" t="s">
+      <c r="AM6" s="40"/>
+      <c r="AN6" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="AO6" s="30"/>
-      <c r="AP6" s="29" t="s">
+      <c r="AO6" s="40"/>
+      <c r="AP6" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="AQ6" s="30"/>
+      <c r="AQ6" s="40"/>
       <c r="AT6" t="s">
         <v>33</v>
       </c>
@@ -2260,7 +2283,7 @@
         <v>2200000</v>
       </c>
       <c r="O9" s="5">
-        <f t="shared" ref="O9:O38" si="2">N9*$E$45</f>
+        <f t="shared" ref="O9:O19" si="2">N9*$E$45</f>
         <v>1320000</v>
       </c>
       <c r="P9" s="5">
@@ -2484,10 +2507,10 @@
         <f>V11*$E$45</f>
         <v>1152000</v>
       </c>
-      <c r="X11" s="65">
+      <c r="X11" s="38">
         <v>2976000</v>
       </c>
-      <c r="Y11" s="65">
+      <c r="Y11" s="38">
         <v>1785000</v>
       </c>
       <c r="Z11" s="5">
@@ -2991,10 +3014,10 @@
         <f t="shared" si="3"/>
         <v>840000</v>
       </c>
-      <c r="R16" s="35" t="s">
+      <c r="R16" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="S16" s="35"/>
+      <c r="S16" s="55"/>
       <c r="T16" s="5">
         <v>1740000</v>
       </c>
@@ -3565,31 +3588,31 @@
       <c r="AP21" s="26"/>
       <c r="AQ21" s="26"/>
     </row>
-    <row r="22" spans="1:47" s="63" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="64"/>
-      <c r="B22" s="57">
+    <row r="22" spans="1:47" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="37"/>
+      <c r="B22" s="30">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="59">
+      <c r="D22" s="32">
         <v>2060000</v>
       </c>
-      <c r="E22" s="59">
+      <c r="E22" s="32">
         <v>1236000</v>
       </c>
-      <c r="F22" s="59">
+      <c r="F22" s="32">
         <v>1630000</v>
       </c>
-      <c r="G22" s="59">
+      <c r="G22" s="32">
         <v>978000</v>
       </c>
-      <c r="H22" s="60">
+      <c r="H22" s="33">
         <v>1490000</v>
       </c>
-      <c r="I22" s="60">
+      <c r="I22" s="33">
         <v>894000</v>
       </c>
       <c r="J22" s="20"/>
@@ -3597,14 +3620,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L22" s="33" t="s">
+      <c r="L22" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="M22" s="34"/>
-      <c r="N22" s="59">
+      <c r="M22" s="57"/>
+      <c r="N22" s="32">
         <v>1280000</v>
       </c>
-      <c r="O22" s="59">
+      <c r="O22" s="32">
         <v>768000</v>
       </c>
       <c r="P22" s="15"/>
@@ -3612,28 +3635,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R22" s="59">
+      <c r="R22" s="32">
         <v>1650000</v>
       </c>
-      <c r="S22" s="59">
+      <c r="S22" s="32">
         <v>990000</v>
       </c>
-      <c r="T22" s="59">
+      <c r="T22" s="32">
         <v>1700000</v>
       </c>
-      <c r="U22" s="59">
+      <c r="U22" s="32">
         <v>1020000</v>
       </c>
-      <c r="V22" s="59">
+      <c r="V22" s="32">
         <v>920000</v>
       </c>
-      <c r="W22" s="59">
+      <c r="W22" s="32">
         <v>552000</v>
       </c>
-      <c r="X22" s="60">
+      <c r="X22" s="33">
         <v>1700000</v>
       </c>
-      <c r="Y22" s="59">
+      <c r="Y22" s="32">
         <v>1020000</v>
       </c>
       <c r="Z22" s="15"/>
@@ -3641,10 +3664,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB22" s="60">
+      <c r="AB22" s="33">
         <v>1370000</v>
       </c>
-      <c r="AC22" s="59">
+      <c r="AC22" s="32">
         <v>822000</v>
       </c>
       <c r="AD22" s="15"/>
@@ -3652,16 +3675,16 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AF22" s="61">
+      <c r="AF22" s="34">
         <v>1130000</v>
       </c>
-      <c r="AG22" s="62">
+      <c r="AG22" s="35">
         <v>678000</v>
       </c>
-      <c r="AH22" s="61">
+      <c r="AH22" s="34">
         <v>1725000</v>
       </c>
-      <c r="AI22" s="61">
+      <c r="AI22" s="34">
         <v>1035000</v>
       </c>
       <c r="AJ22" s="26"/>
@@ -3672,10 +3695,10 @@
       <c r="AO22" s="26"/>
       <c r="AP22" s="26"/>
       <c r="AQ22" s="26"/>
-      <c r="AR22" s="64"/>
-      <c r="AS22" s="64"/>
-      <c r="AT22" s="64"/>
-      <c r="AU22" s="64"/>
+      <c r="AR22" s="37"/>
+      <c r="AS22" s="37"/>
+      <c r="AT22" s="37"/>
+      <c r="AU22" s="37"/>
     </row>
     <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="B23" s="2">
@@ -4177,10 +4200,10 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R27" s="44" t="s">
+      <c r="R27" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="S27" s="45"/>
+      <c r="S27" s="54"/>
       <c r="T27" s="6">
         <v>1810000</v>
       </c>
@@ -4277,10 +4300,10 @@
       <c r="M28" s="7">
         <v>816000</v>
       </c>
-      <c r="N28" s="46" t="s">
+      <c r="N28" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="O28" s="47"/>
+      <c r="O28" s="48"/>
       <c r="P28" s="15"/>
       <c r="Q28" s="14">
         <f t="shared" si="3"/>
@@ -4388,8 +4411,8 @@
       <c r="M29" s="7">
         <v>1002000</v>
       </c>
-      <c r="N29" s="48"/>
-      <c r="O29" s="49"/>
+      <c r="N29" s="49"/>
+      <c r="O29" s="50"/>
       <c r="P29" s="15"/>
       <c r="Q29" s="14">
         <f t="shared" si="3"/>
@@ -4497,8 +4520,8 @@
       <c r="M30" s="7">
         <v>1530000</v>
       </c>
-      <c r="N30" s="48"/>
-      <c r="O30" s="49"/>
+      <c r="N30" s="49"/>
+      <c r="O30" s="50"/>
       <c r="P30" s="15"/>
       <c r="Q30" s="14">
         <f t="shared" si="3"/>
@@ -4544,14 +4567,14 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AF30" s="46" t="s">
+      <c r="AF30" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="AG30" s="47"/>
-      <c r="AH30" s="46" t="s">
+      <c r="AG30" s="48"/>
+      <c r="AH30" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="AI30" s="47"/>
+      <c r="AI30" s="48"/>
       <c r="AJ30" s="6">
         <v>1560000</v>
       </c>
@@ -4602,8 +4625,8 @@
       <c r="M31" s="7">
         <v>880000</v>
       </c>
-      <c r="N31" s="48"/>
-      <c r="O31" s="49"/>
+      <c r="N31" s="49"/>
+      <c r="O31" s="50"/>
       <c r="P31" s="15"/>
       <c r="Q31" s="14">
         <f t="shared" si="3"/>
@@ -4649,10 +4672,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AF31" s="48"/>
-      <c r="AG31" s="49"/>
-      <c r="AH31" s="48"/>
-      <c r="AI31" s="49"/>
+      <c r="AF31" s="49"/>
+      <c r="AG31" s="50"/>
+      <c r="AH31" s="49"/>
+      <c r="AI31" s="50"/>
       <c r="AJ31" s="6">
         <v>2010000</v>
       </c>
@@ -4703,8 +4726,8 @@
       <c r="M32" s="7">
         <v>925000</v>
       </c>
-      <c r="N32" s="48"/>
-      <c r="O32" s="49"/>
+      <c r="N32" s="49"/>
+      <c r="O32" s="50"/>
       <c r="P32" s="15"/>
       <c r="Q32" s="14">
         <f t="shared" si="3"/>
@@ -4746,10 +4769,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AF32" s="48"/>
-      <c r="AG32" s="49"/>
-      <c r="AH32" s="48"/>
-      <c r="AI32" s="49"/>
+      <c r="AF32" s="49"/>
+      <c r="AG32" s="50"/>
+      <c r="AH32" s="49"/>
+      <c r="AI32" s="50"/>
       <c r="AJ32" s="6">
         <v>2370000</v>
       </c>
@@ -4800,8 +4823,8 @@
       <c r="M33" s="7">
         <v>708000</v>
       </c>
-      <c r="N33" s="48"/>
-      <c r="O33" s="49"/>
+      <c r="N33" s="49"/>
+      <c r="O33" s="50"/>
       <c r="P33" s="15"/>
       <c r="Q33" s="14">
         <f t="shared" si="3"/>
@@ -4843,10 +4866,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AF33" s="48"/>
-      <c r="AG33" s="49"/>
-      <c r="AH33" s="48"/>
-      <c r="AI33" s="49"/>
+      <c r="AF33" s="49"/>
+      <c r="AG33" s="50"/>
+      <c r="AH33" s="49"/>
+      <c r="AI33" s="50"/>
       <c r="AJ33" s="6">
         <v>2000000</v>
       </c>
@@ -4874,7 +4897,7 @@
       <c r="E34" s="6">
         <v>1265000</v>
       </c>
-      <c r="F34" s="52">
+      <c r="F34" s="29">
         <v>2190000</v>
       </c>
       <c r="G34" s="27">
@@ -4897,8 +4920,8 @@
       <c r="M34" s="7">
         <v>768000</v>
       </c>
-      <c r="N34" s="48"/>
-      <c r="O34" s="49"/>
+      <c r="N34" s="49"/>
+      <c r="O34" s="50"/>
       <c r="P34" s="15"/>
       <c r="Q34" s="14">
         <f t="shared" si="3"/>
@@ -4940,10 +4963,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AF34" s="50"/>
-      <c r="AG34" s="51"/>
-      <c r="AH34" s="48"/>
-      <c r="AI34" s="49"/>
+      <c r="AF34" s="51"/>
+      <c r="AG34" s="52"/>
+      <c r="AH34" s="49"/>
+      <c r="AI34" s="50"/>
       <c r="AJ34" s="6">
         <v>2100000</v>
       </c>
@@ -4971,7 +4994,7 @@
       <c r="E35" s="6">
         <v>780000</v>
       </c>
-      <c r="F35" s="52">
+      <c r="F35" s="29">
         <v>1710000</v>
       </c>
       <c r="G35" s="27">
@@ -4994,8 +5017,8 @@
       <c r="M35" s="7">
         <v>846000</v>
       </c>
-      <c r="N35" s="48"/>
-      <c r="O35" s="49"/>
+      <c r="N35" s="49"/>
+      <c r="O35" s="50"/>
       <c r="P35" s="15"/>
       <c r="Q35" s="14">
         <f t="shared" si="3"/>
@@ -5026,10 +5049,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB35" s="53" t="s">
+      <c r="AB35" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="AC35" s="54"/>
+      <c r="AC35" s="46"/>
       <c r="AD35" s="15"/>
       <c r="AE35" s="14">
         <f t="shared" si="7"/>
@@ -5041,8 +5064,8 @@
       <c r="AG35" s="23">
         <v>525000</v>
       </c>
-      <c r="AH35" s="48"/>
-      <c r="AI35" s="49"/>
+      <c r="AH35" s="49"/>
+      <c r="AI35" s="50"/>
       <c r="AJ35" s="6">
         <v>3435000</v>
       </c>
@@ -5070,7 +5093,7 @@
       <c r="E36" s="6">
         <v>1110000</v>
       </c>
-      <c r="F36" s="52">
+      <c r="F36" s="29">
         <v>1730000</v>
       </c>
       <c r="G36" s="27">
@@ -5093,8 +5116,8 @@
       <c r="M36" s="7">
         <v>990000</v>
       </c>
-      <c r="N36" s="48"/>
-      <c r="O36" s="49"/>
+      <c r="N36" s="49"/>
+      <c r="O36" s="50"/>
       <c r="P36" s="15"/>
       <c r="Q36" s="14">
         <f t="shared" si="3"/>
@@ -5142,8 +5165,8 @@
       <c r="AG36" s="23">
         <v>880000</v>
       </c>
-      <c r="AH36" s="48"/>
-      <c r="AI36" s="49"/>
+      <c r="AH36" s="49"/>
+      <c r="AI36" s="50"/>
       <c r="AJ36" s="27">
         <v>1840000</v>
       </c>
@@ -5175,7 +5198,7 @@
       <c r="E37" s="6">
         <v>860000</v>
       </c>
-      <c r="F37" s="52">
+      <c r="F37" s="29">
         <v>1140000</v>
       </c>
       <c r="G37" s="27">
@@ -5192,12 +5215,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L37" s="55" t="s">
+      <c r="L37" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="M37" s="56"/>
-      <c r="N37" s="48"/>
-      <c r="O37" s="49"/>
+      <c r="M37" s="44"/>
+      <c r="N37" s="49"/>
+      <c r="O37" s="50"/>
       <c r="P37" s="15"/>
       <c r="Q37" s="14">
         <f t="shared" si="3"/>
@@ -5245,18 +5268,18 @@
       <c r="AG37" s="23">
         <v>865000</v>
       </c>
-      <c r="AH37" s="48"/>
-      <c r="AI37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="50"/>
       <c r="AJ37" s="27">
         <v>3815000</v>
       </c>
       <c r="AK37" s="27">
         <v>1900000</v>
       </c>
-      <c r="AL37" s="53" t="s">
+      <c r="AL37" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="AM37" s="54"/>
+      <c r="AM37" s="46"/>
       <c r="AN37" s="6">
         <v>380000</v>
       </c>
@@ -5270,7 +5293,7 @@
         <v>396000</v>
       </c>
     </row>
-    <row r="38" spans="2:43" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:43" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
         <f t="shared" si="11"/>
         <v>31</v>
@@ -5278,87 +5301,108 @@
       <c r="C38" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D38" s="4"/>
-      <c r="E38" s="5">
-        <f t="shared" ref="E24:E38" si="12">D38*$E$45</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="5">
-        <f t="shared" ref="G24:G38" si="13">F38*$E$45</f>
-        <v>0</v>
-      </c>
-      <c r="H38" s="4"/>
-      <c r="I38" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="D38" s="66">
+        <v>1900000</v>
+      </c>
+      <c r="E38" s="66">
+        <v>950000</v>
+      </c>
+      <c r="F38" s="67">
+        <v>1795000</v>
+      </c>
+      <c r="G38" s="68">
+        <v>900000</v>
+      </c>
+      <c r="H38" s="69">
+        <v>1304000</v>
+      </c>
+      <c r="I38" s="69">
+        <v>783000</v>
       </c>
       <c r="J38" s="20"/>
       <c r="K38" s="14">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="50"/>
-      <c r="O38" s="51"/>
+      <c r="L38" s="66">
+        <v>1720000</v>
+      </c>
+      <c r="M38" s="69">
+        <v>860000</v>
+      </c>
+      <c r="N38" s="51"/>
+      <c r="O38" s="52"/>
       <c r="P38" s="15"/>
       <c r="Q38" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R38" s="4"/>
-      <c r="S38" s="5">
-        <f t="shared" si="9"/>
-        <v>0</v>
+      <c r="R38" s="66">
+        <v>1756000</v>
+      </c>
+      <c r="S38" s="69">
+        <v>878000</v>
       </c>
       <c r="T38" s="15"/>
       <c r="U38" s="15"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="5">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
+      <c r="V38" s="66">
+        <v>1830000</v>
+      </c>
+      <c r="W38" s="66">
+        <v>920000</v>
+      </c>
+      <c r="X38" s="7">
+        <v>750000</v>
+      </c>
+      <c r="Y38" s="4">
+        <v>450000</v>
+      </c>
       <c r="Z38" s="15"/>
       <c r="AA38" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AB38" s="7"/>
-      <c r="AC38" s="7"/>
+      <c r="AB38" s="15"/>
+      <c r="AC38" s="14">
+        <f t="shared" ref="AC38" si="12">AB38*$E$45</f>
+        <v>0</v>
+      </c>
       <c r="AD38" s="15"/>
       <c r="AE38" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AF38" s="21"/>
-      <c r="AG38" s="7">
-        <f t="shared" ref="AG24:AG38" si="14">AF38*$E$45</f>
-        <v>0</v>
-      </c>
-      <c r="AH38" s="50"/>
-      <c r="AI38" s="51"/>
-      <c r="AJ38" s="21"/>
-      <c r="AK38" s="7">
-        <f t="shared" ref="AK24:AK38" si="15">AJ38*$E$45</f>
-        <v>0</v>
-      </c>
-      <c r="AL38" s="21"/>
-      <c r="AM38" s="7">
-        <f t="shared" ref="AM36:AM38" si="16">AL38*$E$45</f>
-        <v>0</v>
-      </c>
-      <c r="AN38" s="21"/>
-      <c r="AO38" s="7">
-        <f t="shared" ref="AO36:AO38" si="17">AN38*$E$45</f>
-        <v>0</v>
-      </c>
-      <c r="AP38" s="21"/>
-      <c r="AQ38" s="7">
-        <f t="shared" ref="AQ38" si="18">AP38*$E$45</f>
-        <v>0</v>
+      <c r="AF38" s="68">
+        <v>1758000</v>
+      </c>
+      <c r="AG38" s="70">
+        <v>879000</v>
+      </c>
+      <c r="AH38" s="51"/>
+      <c r="AI38" s="52"/>
+      <c r="AJ38" s="68">
+        <v>2925000</v>
+      </c>
+      <c r="AK38" s="68">
+        <v>1462000</v>
+      </c>
+      <c r="AL38" s="69">
+        <v>1010000</v>
+      </c>
+      <c r="AM38" s="69">
+        <v>606000</v>
+      </c>
+      <c r="AN38" s="66">
+        <v>2901000</v>
+      </c>
+      <c r="AO38" s="69">
+        <v>1451000</v>
+      </c>
+      <c r="AP38" s="66">
+        <v>990000</v>
+      </c>
+      <c r="AQ38" s="66">
+        <v>594000</v>
       </c>
     </row>
     <row r="45" spans="2:43" x14ac:dyDescent="0.25">
@@ -5371,6 +5415,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="V6:W6"/>
     <mergeCell ref="L37:M37"/>
     <mergeCell ref="AP6:AQ6"/>
     <mergeCell ref="AL37:AM37"/>
@@ -5387,20 +5445,6 @@
     <mergeCell ref="Z6:AA6"/>
     <mergeCell ref="AD6:AE6"/>
     <mergeCell ref="R16:S16"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="T6:U6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5462,34 +5506,34 @@
     </row>
     <row r="5" spans="2:38" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:38" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="29" t="s">
+      <c r="C6" s="65"/>
+      <c r="D6" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="29" t="s">
+      <c r="E6" s="40"/>
+      <c r="F6" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="29" t="s">
+      <c r="G6" s="40"/>
+      <c r="H6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="30"/>
-      <c r="J6" s="29" t="s">
+      <c r="I6" s="40"/>
+      <c r="J6" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="K6" s="30"/>
-      <c r="L6" s="29" t="s">
+      <c r="K6" s="40"/>
+      <c r="L6" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="M6" s="30"/>
-      <c r="N6" s="29" t="s">
+      <c r="M6" s="40"/>
+      <c r="N6" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="O6" s="30"/>
+      <c r="O6" s="40"/>
     </row>
     <row r="7" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
@@ -5970,10 +6014,10 @@
       <c r="E18" s="5">
         <v>1170000</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F18" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="G18" s="37"/>
+      <c r="G18" s="59"/>
       <c r="H18" s="6">
         <v>1860000</v>
       </c>
@@ -6013,8 +6057,8 @@
       <c r="E19" s="6">
         <v>1230000</v>
       </c>
-      <c r="F19" s="38"/>
-      <c r="G19" s="39"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="61"/>
       <c r="H19" s="6">
         <v>1850000</v>
       </c>
@@ -6054,8 +6098,8 @@
       <c r="E20" s="6">
         <v>1170000</v>
       </c>
-      <c r="F20" s="38"/>
-      <c r="G20" s="39"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="61"/>
       <c r="H20" s="6">
         <v>1200000</v>
       </c>
@@ -6095,8 +6139,8 @@
       <c r="E21" s="6">
         <v>780000</v>
       </c>
-      <c r="F21" s="38"/>
-      <c r="G21" s="39"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="61"/>
       <c r="H21" s="6">
         <v>2400000</v>
       </c>
@@ -6132,8 +6176,8 @@
       <c r="E22" s="6">
         <v>1140000</v>
       </c>
-      <c r="F22" s="38"/>
-      <c r="G22" s="39"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="61"/>
       <c r="H22" s="12"/>
       <c r="I22" s="5"/>
       <c r="J22" s="4"/>
@@ -6161,8 +6205,8 @@
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="39"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="61"/>
       <c r="H23" s="4"/>
       <c r="I23" s="5"/>
       <c r="J23" s="4"/>
@@ -6182,8 +6226,8 @@
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="5"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="39"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="61"/>
       <c r="H24" s="4"/>
       <c r="I24" s="5"/>
       <c r="J24" s="4"/>
@@ -6203,8 +6247,8 @@
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="39"/>
+      <c r="F25" s="60"/>
+      <c r="G25" s="61"/>
       <c r="H25" s="4"/>
       <c r="I25" s="5"/>
       <c r="J25" s="4"/>
@@ -6224,8 +6268,8 @@
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="5"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="39"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="61"/>
       <c r="H26" s="4"/>
       <c r="I26" s="5"/>
       <c r="J26" s="4"/>
@@ -6245,8 +6289,8 @@
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="5"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="39"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="61"/>
       <c r="H27" s="4"/>
       <c r="I27" s="5"/>
       <c r="J27" s="4"/>
@@ -6266,8 +6310,8 @@
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="5"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="39"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="61"/>
       <c r="H28" s="4"/>
       <c r="I28" s="5"/>
       <c r="J28" s="4"/>
@@ -6287,8 +6331,8 @@
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="5"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="39"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="61"/>
       <c r="H29" s="4"/>
       <c r="I29" s="5"/>
       <c r="J29" s="4"/>
@@ -6308,8 +6352,8 @@
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="5"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="39"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="61"/>
       <c r="H30" s="4"/>
       <c r="I30" s="5"/>
       <c r="J30" s="4"/>
@@ -6329,8 +6373,8 @@
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="5"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="39"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="61"/>
       <c r="H31" s="4"/>
       <c r="I31" s="5"/>
       <c r="J31" s="4"/>
@@ -6350,8 +6394,8 @@
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="5"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="39"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="61"/>
       <c r="H32" s="4"/>
       <c r="I32" s="5"/>
       <c r="J32" s="4"/>
@@ -6371,8 +6415,8 @@
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="5"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="39"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="61"/>
       <c r="H33" s="4"/>
       <c r="I33" s="5"/>
       <c r="J33" s="4"/>
@@ -6392,8 +6436,8 @@
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="5"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="39"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="61"/>
       <c r="H34" s="4"/>
       <c r="I34" s="5"/>
       <c r="J34" s="4"/>
@@ -6413,8 +6457,8 @@
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="5"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="39"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="61"/>
       <c r="H35" s="4"/>
       <c r="I35" s="5"/>
       <c r="J35" s="4"/>
@@ -6434,8 +6478,8 @@
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="5"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="39"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="61"/>
       <c r="H36" s="4"/>
       <c r="I36" s="5"/>
       <c r="J36" s="4"/>
@@ -6455,8 +6499,8 @@
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="5"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="39"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="61"/>
       <c r="H37" s="4"/>
       <c r="I37" s="5"/>
       <c r="J37" s="4"/>
@@ -6476,8 +6520,8 @@
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="5"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="41"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="63"/>
       <c r="H38" s="4"/>
       <c r="I38" s="5"/>
       <c r="J38" s="4"/>
